--- a/docs/oc-regiones/suministro-de-combustibles/atacama.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M227"/>
+  <dimension ref="A1:M228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4809.25</v>
+        <v>4761.25</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2491.85</v>
+        <v>2466.98</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2864.06</v>
+        <v>2848.38</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4695.96</v>
+        <v>4670.24</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2244.32</v>
+        <v>2241.46</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6412.33</v>
+        <v>6404.17</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5343.61</v>
+        <v>5362.68</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2778.68</v>
+        <v>2788.59</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2244.32</v>
+        <v>2251.7</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10687.21</v>
+        <v>10722.37</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>22443.15</v>
+        <v>22516.97</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>26718.04</v>
+        <v>26903.13</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4068.3</v>
+        <v>4087.25</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8549.77</v>
+        <v>8589.59</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6412.33</v>
+        <v>6458.56</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4103.89</v>
+        <v>4133.48</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2244.32</v>
+        <v>2255.91</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9823.58</v>
+        <v>9696.6</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3820.28</v>
+        <v>3770.9</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2292.17</v>
+        <v>2263.05</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4801.55</v>
+        <v>4740.56</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>11482.67</v>
+        <v>11336.82</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2277.17</v>
+        <v>2254.51</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3274.53</v>
+        <v>3262.78</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>14899.1</v>
+        <v>14845.67</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7640.56</v>
+        <v>7624.03</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2837.92</v>
+        <v>2831.78</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3056.22</v>
+        <v>3043.41</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2866.85</v>
+        <v>2877.85</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>13098.11</v>
+        <v>13148.38</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5457.54</v>
+        <v>5478.49</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6549.05</v>
+        <v>6574.19</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>27287.72</v>
+        <v>27392.46</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8732.07</v>
+        <v>8719.82</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3681.29</v>
+        <v>3686.01</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2292.17</v>
+        <v>2295.11</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4911.79</v>
+        <v>4945.6</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>13016.54</v>
+        <v>13106.13</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4147.73</v>
+        <v>4176.28</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>24186.74</v>
+        <v>24393.44</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>22921.69</v>
+        <v>23117.57</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2933.35</v>
+        <v>2964.81</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2278.26</v>
+        <v>2306.26</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13098.11</v>
+        <v>13169.74</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>21830.18</v>
+        <v>21949.56</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>54575.44</v>
+        <v>54873.9</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4525.06</v>
+        <v>4436.8</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2828.16</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4038.62</v>
+        <v>3944.14</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2828.16</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3393.8</v>
+        <v>3350.72</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4977.57</v>
+        <v>4913.24</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5854.3</v>
+        <v>5842.77</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9050.18</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3393.8</v>
+        <v>3398.51</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9615.76</v>
+        <v>9609.190000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5656.33</v>
+        <v>5626.45</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3167.54</v>
+        <v>3150.81</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3393.8</v>
+        <v>3416.04</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2941.29</v>
+        <v>2960.57</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6787.59</v>
+        <v>6879</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4978.7</v>
+        <v>5054.5</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6787.59</v>
+        <v>6952.65</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5656.33</v>
+        <v>5827.85</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>14706.45</v>
+        <v>15152.4</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8484.49</v>
+        <v>8741.77</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>26584.74</v>
+        <v>27390.87</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3393.8</v>
+        <v>3494.67</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4640.26</v>
+        <v>4623.74</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>11554.26</v>
+        <v>11613.94</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9241.4</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>29001.65</v>
+        <v>28879.37</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5106.61</v>
+        <v>5120.63</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3016.17</v>
+        <v>3043.61</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2668.15</v>
+        <v>2692.42</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2436.14</v>
+        <v>2453.1</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>58003.29</v>
+        <v>57903.88</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3480.2</v>
+        <v>3474.23</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>13920.79</v>
+        <v>13821.06</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4640.26</v>
+        <v>4612.92</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>6960.4</v>
+        <v>6919.38</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2900.16</v>
+        <v>2882.54</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4640.26</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>15080.86</v>
+        <v>15158.94</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3248.18</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>23201.32</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>7693.21</v>
+        <v>7723.54</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4839.03</v>
+        <v>4858.11</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>10990.3</v>
+        <v>11171.44</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>26376.72</v>
+        <v>26811.45</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>11739.04</v>
+        <v>11932.51</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>27475.75</v>
+        <v>27906.15</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.35</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>5495.15</v>
+        <v>5470.58</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2307.96</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3316.87</v>
+        <v>3330.57</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2857.48</v>
+        <v>2849.6</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>6594.18</v>
+        <v>6575.99</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>22112.49</v>
+        <v>21985.47</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>16485.45</v>
+        <v>16390.76</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4840.13</v>
+        <v>4812.33</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>6594.18</v>
+        <v>6556.3</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5495.15</v>
+        <v>5463.59</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>15386.42</v>
+        <v>15287.85</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>6594.18</v>
+        <v>6551.94</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2527.77</v>
+        <v>2491.2</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2747.58</v>
+        <v>2707.83</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3341.18</v>
+        <v>3234.64</v>
       </c>
     </row>
     <row r="114">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>37866.71</v>
+        <v>36869.56</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3703-174-CM26</t>
+          <t>1556-96-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7427,17 +7427,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5791.38</v>
+        <v>3795.4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1556-96-CM26</t>
+          <t>3703-174-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7488,17 +7488,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3898.04</v>
+        <v>5638.87</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3118.44</v>
+        <v>3061.88</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2784.32</v>
+        <v>2733.82</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2450.2</v>
+        <v>2405.77</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2450.2</v>
+        <v>2384.59</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3341.18</v>
+        <v>3251.72</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2450.2</v>
+        <v>2457.33</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>36953.46</v>
+        <v>37107.04</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2895.69</v>
+        <v>2920.27</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>17697.12</v>
+        <v>17667.53</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3341.18</v>
+        <v>3335.59</v>
       </c>
     </row>
     <row r="127">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5568.63</v>
+        <v>5637.17</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1376-232-CM26</t>
+          <t>707416-29-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2338.83</v>
+        <v>9026.09</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>707416-29-CM26</t>
+          <t>1376-232-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>8909.82</v>
+        <v>2369.35</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3341.18</v>
+        <v>3423.41</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>4176.48</v>
+        <v>4255.46</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>6014.13</v>
+        <v>6127.87</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4454.91</v>
+        <v>4505.57</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5568.63</v>
+        <v>5631.96</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>16705.9</v>
+        <v>16758.47</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>5568.63</v>
+        <v>5586.16</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3898.04</v>
+        <v>3914.2</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>6682.36</v>
+        <v>6710.06</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3563.93</v>
+        <v>3571.31</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3341.18</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="141">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4009.42</v>
+        <v>4017.72</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1554-763-CM26</t>
+          <t>4355-403-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9074,17 +9074,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3976</v>
+        <v>4435.77</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4355-403-CM26</t>
+          <t>1554-763-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9135,17 +9135,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4454.91</v>
+        <v>3958.92</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2381-544-CM26</t>
+          <t>1552-177-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,17 +9196,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>16710.52</v>
+        <v>8305.190000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4484-44-CM26</t>
+          <t>2381-544-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4456.14</v>
+        <v>16610.38</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1552-177-CM26</t>
+          <t>4484-44-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8355.26</v>
+        <v>4429.43</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2785.09</v>
+        <v>2747.22</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>6461.4</v>
+        <v>6373.56</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>38991.22</v>
+        <v>38658.66</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>4456.14</v>
+        <v>4418.13</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>37877.19</v>
+        <v>38164.08</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>55701.75</v>
+        <v>56123.65</v>
       </c>
     </row>
     <row r="153">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>14482.45</v>
+        <v>14592.15</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>952751-110-CM26</t>
+          <t>1554-815-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9806,17 +9806,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4099.65</v>
+        <v>17623.71</v>
       </c>
     </row>
     <row r="155">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>4456.14</v>
+        <v>4473.02</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1554-815-CM26</t>
+          <t>952751-110-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9928,17 +9928,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>17557.19</v>
+        <v>4115.18</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2562.28</v>
+        <v>2555.81</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.17</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>6962.72</v>
+        <v>6893.28</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2450.88</v>
+        <v>2424.22</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5570.17</v>
+        <v>5509.58</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2450.88</v>
+        <v>2424.22</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2361.75</v>
+        <v>2336.06</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>22280.7</v>
+        <v>22038.32</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>14036.84</v>
+        <v>14004.98</v>
       </c>
     </row>
     <row r="166">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>23394.73</v>
+        <v>23336.96</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2859-431-CM26</t>
+          <t>873-16-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2896.49</v>
+        <v>3129.65</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1638-271-CM26</t>
+          <t>4355-503-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10660,17 +10660,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.250.500-k</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3342.1</v>
+        <v>4470.92</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>696011-24-CM26</t>
+          <t>1638-271-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10721,17 +10721,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.250.500-k</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4351.42</v>
+        <v>3353.19</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4355-503-CM26</t>
+          <t>696011-24-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>4456.14</v>
+        <v>4365.86</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>873-16-CM26</t>
+          <t>2859-431-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3119.3</v>
+        <v>2906.1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2923-408-CM26</t>
+          <t>1376-359-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>17824.56</v>
+        <v>8959.67</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2923-409-CM26</t>
+          <t>1558-183-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3342.1</v>
+        <v>4031.85</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1558-183-CM26</t>
+          <t>2923-408-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>4010.53</v>
+        <v>17919.34</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1376-359-CM26</t>
+          <t>2923-409-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3874.32</v>
+        <v>3919.77</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>7029.12</v>
+        <v>7111.58</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3874.32</v>
+        <v>3913.72</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>11069.49</v>
+        <v>11182.06</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>37636.25</v>
+        <v>37102.11</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>6641.69</v>
+        <v>6550.43</v>
       </c>
     </row>
     <row r="182">
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>4427.79</v>
+        <v>4366.96</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1228-15-CM26</t>
+          <t>5350-1040-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11575,17 +11575,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>60.804.005-6</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE CHAÑARAL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2767.37</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5350-1040-CM26</t>
+          <t>2914-113-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11636,17 +11636,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.250.500-k</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3874.32</v>
+        <v>30692.39</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2914-113-CM26</t>
+          <t>1228-15-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11702,12 +11702,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.250.500-k</t>
+          <t>60.804.005-6</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+          <t>ADMINISTRACIÓN ADUANA DE CHAÑARAL</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>30883.87</v>
+        <v>2750.21</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4484-64-CM26</t>
+          <t>3703-333-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>6641.69</v>
+        <v>7062.16</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3703-333-CM26</t>
+          <t>4484-64-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>7030.23</v>
+        <v>6671.86</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4355-589-CM26</t>
+          <t>952751-151-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4427.79</v>
+        <v>8425.74</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>952751-150-CM26</t>
+          <t>4355-589-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>4493.73</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>952751-151-CM26</t>
+          <t>952751-150-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>8425.74</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3985.02</v>
+        <v>4074.89</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3034.12</v>
+        <v>3102.54</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>23245.92</v>
+        <v>23184.44</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4040.36</v>
+        <v>3986.54</v>
       </c>
     </row>
     <row r="195">
@@ -12342,13 +12342,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>5534.74</v>
+        <v>5426.41</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>233-29-CM26</t>
+          <t>4355-643-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3874.32</v>
+        <v>4362.19</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1556-175-CM26</t>
+          <t>1557-237-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>3320.85</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1557-237-CM26</t>
+          <t>1556-175-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>5534.74</v>
+        <v>3271.64</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4355-643-CM26</t>
+          <t>233-29-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12556,12 +12556,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>4427.79</v>
+        <v>3816.92</v>
       </c>
     </row>
     <row r="200">
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>8855.59</v>
+        <v>8673.59</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3703-368-CM26</t>
+          <t>4192-70-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>6822.99</v>
+        <v>32548.55</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1638-329-CM26</t>
+          <t>2923-488-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12734,17 +12734,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.250.500-k</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>3222.45</v>
+        <v>2712.38</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2923-487-CM26</t>
+          <t>3703-368-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>16112.23</v>
+        <v>6891.61</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2923-488-CM26</t>
+          <t>1638-329-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12856,17 +12856,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.250.500-k</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2685.37</v>
+        <v>3254.86</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4192-70-CM26</t>
+          <t>2923-487-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12917,17 +12917,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>32224.45</v>
+        <v>16274.28</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>12889.78</v>
+        <v>13018.86</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>4833.67</v>
+        <v>4809.18</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>9426.52</v>
+        <v>9378.77</v>
       </c>
     </row>
     <row r="209">
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>4833.67</v>
+        <v>4843.97</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4355-688-CM26</t>
+          <t>1556-196-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13222,17 +13222,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>4296.59</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1556-196-CM26</t>
+          <t>4355-688-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13283,17 +13283,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3222.45</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="212">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>3866.93</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>904-106-CM26</t>
+          <t>2380-1316-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>16304.85</v>
+        <v>36405.69</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1729-297-CM26</t>
+          <t>3703-389-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>22557.12</v>
+        <v>7495.29</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3703-389-CM26</t>
+          <t>1729-297-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>7519.04</v>
+        <v>22485.87</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2380-1316-CM26</t>
+          <t>904-106-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13588,17 +13588,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>36521.05</v>
+        <v>16253.34</v>
       </c>
     </row>
     <row r="217">
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2363.13</v>
+        <v>2357.98</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>411-322-CM26</t>
+          <t>2381-858-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13715,12 +13715,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>10741.48</v>
+        <v>21439.9</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2381-858-CM26</t>
+          <t>411-322-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>21482.97</v>
+        <v>10719.95</v>
       </c>
     </row>
     <row r="220">
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2309.42</v>
+        <v>2304.79</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1373324-56-CM26</t>
+          <t>904-115-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2363.13</v>
+        <v>10400.26</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>904-115-CM26</t>
+          <t>1373324-56-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13954,17 +13954,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>10569.73</v>
+        <v>2325.24</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2309.42</v>
+        <v>2272.39</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2363.13</v>
+        <v>2350.03</v>
       </c>
     </row>
     <row r="225">
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3834.71</v>
+        <v>3813.45</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1556-214-CM26</t>
+          <t>1376-533-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14203,12 +14203,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>3222.45</v>
+        <v>6488.03</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1376-533-CM26</t>
+          <t>1556-214-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14294,7 +14294,68 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>6444.89</v>
+        <v>3244.01</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1490607-13-CM26</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="n">
+        <v>24489.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/atacama.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/atacama.xlsx
@@ -562,7 +562,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +24027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +24092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +24157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +24222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +24352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +25002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +25067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +25132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +25197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +25262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +26042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +26107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +26172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +26237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +26302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +27017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +27082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +27147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +27212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +27277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +27342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27992,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +28057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +28122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +28187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +28252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +28317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +28382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +29032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +29097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +29162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +29227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +29292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +29357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +30007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +30072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +30137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +30202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +30267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +30332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +30397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +31047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +31112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +31177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +31242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +31307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +31372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +31697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +32022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +32087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +32152,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +32217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +32282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +32347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +32412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/suministro-de-combustibles/atacama.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M497"/>
+  <dimension ref="A1:M522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1229,7 +1229,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3332-11-CM25</t>
+          <t>873-4-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1249,17 +1249,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2226.5</v>
+        <v>6072.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2923-54-CM25</t>
+          <t>2923-55-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8096.35</v>
+        <v>3036.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2923-55-CM25</t>
+          <t>3332-11-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3036.13</v>
+        <v>2226.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>873-4-CM25</t>
+          <t>2923-54-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6072.26</v>
+        <v>8096.35</v>
       </c>
     </row>
     <row r="17">
@@ -1814,7 +1814,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4484-34-CM25</t>
+          <t>1558-34-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6200.97</v>
+        <v>2687.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1558-34-CM25</t>
+          <t>4484-34-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2687.09</v>
+        <v>6200.97</v>
       </c>
     </row>
     <row r="24">
@@ -2074,7 +2074,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>751-40-CM25</t>
+          <t>411-88-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>411-88-CM25</t>
+          <t>751-40-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1552-4643-CM25</t>
+          <t>1088-3-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5279.11</v>
+        <v>2373.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1088-3-CM25</t>
+          <t>1552-4643-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2373.83</v>
+        <v>5279.11</v>
       </c>
     </row>
     <row r="33">
@@ -3634,7 +3634,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1556-56-CM25</t>
+          <t>2172-6-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2573.92</v>
+        <v>2233.57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2172-6-CM25</t>
+          <t>1556-56-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2233.57</v>
+        <v>2573.92</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1376-183-CM25</t>
+          <t>1088-21-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2688.32</v>
+        <v>6733.42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1671-51-CM25</t>
+          <t>1376-183-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7581.34</v>
+        <v>2688.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1088-21-CM25</t>
+          <t>1671-51-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>6733.42</v>
+        <v>7581.34</v>
       </c>
     </row>
     <row r="55">
@@ -4219,7 +4219,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2923-180-CM25</t>
+          <t>707416-29-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8393.93</v>
+        <v>10492.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5350-3110-CM25</t>
+          <t>1557-105-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4304,17 +4304,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2518.18</v>
+        <v>6295.45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1557-105-CM25</t>
+          <t>2923-180-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6295.45</v>
+        <v>8393.93</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>707416-29-CM25</t>
+          <t>5350-3110-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4434,17 +4434,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>10492.41</v>
+        <v>2518.18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2380-570-CM25</t>
+          <t>1376-221-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4499,17 +4499,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>21135.39</v>
+        <v>4227.08</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1376-221-CM25</t>
+          <t>2380-570-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4227.08</v>
+        <v>21135.39</v>
       </c>
     </row>
     <row r="65">
@@ -5519,7 +5519,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1088-45-CM25</t>
+          <t>2859-284-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2430.74</v>
+        <v>2119.63</v>
       </c>
     </row>
     <row r="80">
@@ -5649,7 +5649,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2859-284-CM25</t>
+          <t>1088-45-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2119.63</v>
+        <v>2430.74</v>
       </c>
     </row>
     <row r="82">
@@ -6299,7 +6299,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4357-180-CM25</t>
+          <t>2380-908-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2644.27</v>
+        <v>21154.17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2380-908-CM25</t>
+          <t>4357-180-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6404,12 +6404,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>21154.17</v>
+        <v>2644.27</v>
       </c>
     </row>
     <row r="93">
@@ -6884,7 +6884,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5349-917-CM25</t>
+          <t>1554-1022-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>5306.67</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4192-2874-CM25</t>
+          <t>5349-917-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>31840.04</v>
+        <v>5306.67</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1554-1022-CM25</t>
+          <t>4192-2874-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3184</v>
+        <v>31840.04</v>
       </c>
     </row>
     <row r="103">
@@ -7209,7 +7209,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>873-36-CM25</t>
+          <t>4484-162-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2240.31</v>
+        <v>6400.89</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4484-162-CM25</t>
+          <t>873-36-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7294,17 +7294,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6400.89</v>
+        <v>2240.31</v>
       </c>
     </row>
     <row r="107">
@@ -7664,7 +7664,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3703-265-CM25</t>
+          <t>1554-1149-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7684,17 +7684,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4676.18</v>
+        <v>10746.03</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1376-434-CM25</t>
+          <t>3703-265-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7749,17 +7749,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6402.8</v>
+        <v>4676.18</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1554-1149-CM25</t>
+          <t>1376-434-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>10746.03</v>
+        <v>6402.8</v>
       </c>
     </row>
     <row r="115">
@@ -7924,7 +7924,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5350-3326-CM25</t>
+          <t>1088-74-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7944,17 +7944,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7983,13 +7983,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2990.3</v>
+        <v>5233.03</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1088-74-CM25</t>
+          <t>5350-3326-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8009,17 +8009,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>5233.03</v>
+        <v>2990.3</v>
       </c>
     </row>
     <row r="118">
@@ -8119,7 +8119,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4357-271-CM25</t>
+          <t>3332-70-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8178,13 +8178,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2661.58</v>
+        <v>2342.19</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3332-70-CM25</t>
+          <t>4357-271-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2342.19</v>
+        <v>2661.58</v>
       </c>
     </row>
     <row r="121">
@@ -8314,7 +8314,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5349-1127-CM25</t>
+          <t>1424-14-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.701.010-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6314.73</v>
+        <v>8419.629999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1424-14-CM25</t>
+          <t>2859-678-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.701.010-2</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>8419.629999999999</v>
+        <v>2210.15</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2859-678-CM25</t>
+          <t>5349-1127-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2210.15</v>
+        <v>6314.73</v>
       </c>
     </row>
     <row r="125">
@@ -9094,7 +9094,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4355-775-CM25</t>
+          <t>4355-769-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3722.3</v>
+        <v>2558.75</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4355-769-CM25</t>
+          <t>4355-775-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2558.75</v>
+        <v>3722.3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1613-43-CM25</t>
+          <t>1558-174-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9244,17 +9244,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2180.68</v>
+        <v>2741.66</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1558-174-CM25</t>
+          <t>1613-43-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9309,17 +9309,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2741.66</v>
+        <v>2180.68</v>
       </c>
     </row>
     <row r="138">
@@ -10459,7 +10459,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3332-86-CM25</t>
+          <t>2381-1026-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10518,13 +10518,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2249.33</v>
+        <v>10224.22</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2381-1026-CM25</t>
+          <t>3332-86-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>10224.22</v>
+        <v>2249.33</v>
       </c>
     </row>
     <row r="157">
@@ -11239,7 +11239,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1556-190-CM25</t>
+          <t>1376-618-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2152.13</v>
+        <v>6238.04</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1376-618-CM25</t>
+          <t>1556-190-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>6238.04</v>
+        <v>2152.13</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4357-383-CM25</t>
+          <t>5349-1664-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11389,17 +11389,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2587.35</v>
+        <v>6209.64</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5349-1664-CM25</t>
+          <t>4357-383-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11454,17 +11454,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6209.64</v>
+        <v>2587.35</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3703-390-CM25</t>
+          <t>5350-3592-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11558,13 +11558,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>4555.97</v>
+        <v>2905.86</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5350-3592-CM25</t>
+          <t>3703-390-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11623,7 +11623,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2905.86</v>
+        <v>4555.97</v>
       </c>
     </row>
     <row r="173">
@@ -11954,7 +11954,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2923-484-CM25</t>
+          <t>2923-485-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12013,13 +12013,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>9323.719999999999</v>
+        <v>2589.92</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2923-485-CM25</t>
+          <t>2923-484-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2589.92</v>
+        <v>9323.719999999999</v>
       </c>
     </row>
     <row r="180">
@@ -12279,7 +12279,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4355-992-CM25</t>
+          <t>873-47-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12299,17 +12299,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12319,12 +12319,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12338,13 +12338,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3457.41</v>
+        <v>3094.51</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>873-47-CM25</t>
+          <t>2859-1049-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12384,12 +12384,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3094.51</v>
+        <v>2166.15</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2859-1049-CM25</t>
+          <t>4355-992-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12429,17 +12429,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2166.15</v>
+        <v>3457.41</v>
       </c>
     </row>
     <row r="186">
@@ -12539,7 +12539,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4355-1045-CM25</t>
+          <t>1558-248-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12559,17 +12559,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12598,13 +12598,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2585.13</v>
+        <v>2688.53</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1558-248-CM25</t>
+          <t>4355-1045-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12624,17 +12624,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12663,7 +12663,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2688.53</v>
+        <v>2585.13</v>
       </c>
     </row>
     <row r="189">
@@ -12734,7 +12734,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5350-3677-CM25</t>
+          <t>3332-111-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12793,13 +12793,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2908.4</v>
+        <v>2285.17</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3332-111-CM25</t>
+          <t>5350-3677-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2285.17</v>
+        <v>2908.4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1554-1595-CM25</t>
+          <t>5349-1896-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12923,13 +12923,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3139.82</v>
+        <v>6279.63</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5349-1896-CM25</t>
+          <t>1554-1595-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>6279.63</v>
+        <v>3139.82</v>
       </c>
     </row>
     <row r="194">
@@ -13124,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2172-19-CM25</t>
+          <t>1376-724-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13164,12 +13164,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13183,13 +13183,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2181.73</v>
+        <v>2623.65</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1376-724-CM25</t>
+          <t>2172-19-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13214,12 +13214,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13229,12 +13229,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13248,7 +13248,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2623.65</v>
+        <v>2181.73</v>
       </c>
     </row>
     <row r="198">
@@ -13384,7 +13384,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1552-5116-CM25</t>
+          <t>1028871-1338-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13443,13 +13443,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>11471.48</v>
+        <v>3128.58</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1028871-1338-CM25</t>
+          <t>1552-5116-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13508,7 +13508,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3128.58</v>
+        <v>11471.48</v>
       </c>
     </row>
     <row r="202">
@@ -13579,7 +13579,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2923-558-CM25</t>
+          <t>1557-327-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13599,17 +13599,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13638,13 +13638,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>9382.92</v>
+        <v>5212.73</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1557-327-CM25</t>
+          <t>4357-438-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13664,17 +13664,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13703,13 +13703,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>5212.73</v>
+        <v>2606.37</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4357-438-CM25</t>
+          <t>2923-558-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13768,7 +13768,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2606.37</v>
+        <v>9382.92</v>
       </c>
     </row>
     <row r="206">
@@ -14034,7 +14034,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2859-1246-CM25</t>
+          <t>4355-1122-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14054,17 +14054,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14093,13 +14093,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2180.48</v>
+        <v>2595.81</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4355-1122-CM25</t>
+          <t>2859-1246-CM25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14139,12 +14139,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14158,7 +14158,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2595.81</v>
+        <v>2180.48</v>
       </c>
     </row>
     <row r="212">
@@ -14814,7 +14814,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1424-29-CM25</t>
+          <t>1376-823-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>60.701.010-2</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14873,13 +14873,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2644.55</v>
+        <v>6346.92</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1376-823-CM25</t>
+          <t>1424-29-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.701.010-2</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>6346.92</v>
+        <v>2644.55</v>
       </c>
     </row>
     <row r="224">
@@ -15724,7 +15724,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5349-2380-CM25</t>
+          <t>1346283-248-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15783,13 +15783,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>6404.17</v>
+        <v>2241.46</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1346283-248-CM25</t>
+          <t>5349-2380-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15848,7 +15848,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2241.46</v>
+        <v>6404.17</v>
       </c>
     </row>
     <row r="238">
@@ -16244,7 +16244,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1088-162-CM25</t>
+          <t>1088-164-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>8589.59</v>
+        <v>4087.25</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1088-164-CM25</t>
+          <t>1088-162-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>4087.25</v>
+        <v>8589.59</v>
       </c>
     </row>
     <row r="246">
@@ -16439,7 +16439,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1248-22-CM25</t>
+          <t>1376-910-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16459,17 +16459,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>60.805.004-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>4133.48</v>
+        <v>6458.56</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1376-910-CM25</t>
+          <t>1248-22-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16524,17 +16524,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.805.004-3</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,7 +16563,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>6458.56</v>
+        <v>4133.48</v>
       </c>
     </row>
     <row r="249">
@@ -16634,7 +16634,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2923-688-CM25</t>
+          <t>2923-687-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16693,13 +16693,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>3770.9</v>
+        <v>9696.6</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2923-687-CM25</t>
+          <t>2923-688-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>9696.6</v>
+        <v>3770.9</v>
       </c>
     </row>
     <row r="252">
@@ -17349,7 +17349,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1088-194-CM25</t>
+          <t>1133261-205-CM25</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17374,12 +17374,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2877.85</v>
+        <v>13148.38</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1133261-205-CM25</t>
+          <t>1133261-206-CM25</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>13148.38</v>
+        <v>5478.49</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1133261-206-CM25</t>
+          <t>5349-2635-CM25</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17538,13 +17538,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>5478.49</v>
+        <v>6574.19</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5349-2635-CM25</t>
+          <t>2380-2818-CM25</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17564,17 +17564,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -17603,13 +17603,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>6574.19</v>
+        <v>27392.46</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2380-2818-CM25</t>
+          <t>1088-194-CM25</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17629,17 +17629,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17649,12 +17649,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>27392.46</v>
+        <v>2877.85</v>
       </c>
     </row>
     <row r="266">
@@ -17869,7 +17869,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>651-2598-CM25</t>
+          <t>3703-666-CM25</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17894,12 +17894,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17928,13 +17928,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>13106.13</v>
+        <v>4176.28</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3703-666-CM25</t>
+          <t>1088-196-CM25</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17954,17 +17954,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,13 +17993,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>4176.28</v>
+        <v>4945.6</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1088-196-CM25</t>
+          <t>651-2598-CM25</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18019,17 +18019,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18058,7 +18058,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>4945.6</v>
+        <v>13106.13</v>
       </c>
     </row>
     <row r="272">
@@ -20209,7 +20209,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1729-62-CM26</t>
+          <t>2380-195-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20234,12 +20234,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20268,13 +20268,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>9241.4</v>
+        <v>28879.37</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2380-195-CM26</t>
+          <t>1729-62-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20299,12 +20299,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>28879.37</v>
+        <v>9241.4</v>
       </c>
     </row>
     <row r="307">
@@ -20599,7 +20599,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1556-49-CM26</t>
+          <t>4192-12-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20624,12 +20624,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20658,13 +20658,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>3474.23</v>
+        <v>57903.88</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4192-12-CM26</t>
+          <t>1556-49-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20689,12 +20689,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20723,7 +20723,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>57903.88</v>
+        <v>3474.23</v>
       </c>
     </row>
     <row r="313">
@@ -21054,7 +21054,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2923-123-CM26</t>
+          <t>5350-693-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -21074,17 +21074,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>15158.94</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5350-693-CM26</t>
+          <t>2923-123-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21139,17 +21139,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21178,7 +21178,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>3265</v>
+        <v>15158.94</v>
       </c>
     </row>
     <row r="320">
@@ -21249,7 +21249,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1671-31-CM26</t>
+          <t>3703-148-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21269,17 +21269,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21308,13 +21308,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>7723.54</v>
+        <v>4858.11</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3703-148-CM26</t>
+          <t>1671-31-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21334,17 +21334,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -21373,13 +21373,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>4858.11</v>
+        <v>7723.54</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2381-271-CM26</t>
+          <t>846-11-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21399,17 +21399,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>11171.44</v>
+        <v>11932.51</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1729-104-CM26</t>
+          <t>2381-271-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21469,12 +21469,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21503,13 +21503,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>26811.45</v>
+        <v>11171.44</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>846-11-CM26</t>
+          <t>1729-104-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21529,17 +21529,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21568,7 +21568,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>11932.51</v>
+        <v>26811.45</v>
       </c>
     </row>
     <row r="326">
@@ -21639,7 +21639,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5349-530-CM26</t>
+          <t>1556-75-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21664,12 +21664,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21698,13 +21698,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>5470.58</v>
+        <v>3282.35</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1556-75-CM26</t>
+          <t>5349-530-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21763,7 +21763,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>3282.35</v>
+        <v>5470.58</v>
       </c>
     </row>
     <row r="329">
@@ -21899,7 +21899,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1558-102-CM26</t>
+          <t>2926-38-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21924,12 +21924,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21958,13 +21958,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2849.6</v>
+        <v>6575.99</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2926-38-CM26</t>
+          <t>1558-102-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21989,12 +21989,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>6575.99</v>
+        <v>2849.6</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>3703-163-CM26</t>
+          <t>1554-537-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22049,17 +22049,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22088,7 +22088,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>4812.33</v>
+        <v>21985.47</v>
       </c>
     </row>
     <row r="334">
@@ -22159,7 +22159,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1554-537-CM26</t>
+          <t>3703-163-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22179,17 +22179,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>21985.47</v>
+        <v>4812.33</v>
       </c>
     </row>
     <row r="336">
@@ -22549,7 +22549,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3703-174-CM26</t>
+          <t>1556-96-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22569,17 +22569,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22608,13 +22608,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>5638.87</v>
+        <v>3795.4</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1556-96-CM26</t>
+          <t>2380-618-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22634,17 +22634,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22673,13 +22673,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>3795.4</v>
+        <v>36869.56</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2380-618-CM26</t>
+          <t>3703-174-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22704,12 +22704,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22738,13 +22738,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>36869.56</v>
+        <v>5638.87</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1346283-68-CM26</t>
+          <t>5350-816-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22764,17 +22764,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2405.77</v>
+        <v>3061.88</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5350-816-CM26</t>
+          <t>4357-94-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22834,12 +22834,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22868,13 +22868,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>3061.88</v>
+        <v>2733.82</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>4357-94-CM26</t>
+          <t>1346283-68-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22894,17 +22894,17 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22933,7 +22933,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2733.82</v>
+        <v>2405.77</v>
       </c>
     </row>
     <row r="347">
@@ -23459,7 +23459,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>707416-29-CM26</t>
+          <t>1376-232-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23518,13 +23518,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>9026.09</v>
+        <v>2369.35</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1376-232-CM26</t>
+          <t>707416-29-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23583,7 +23583,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2369.35</v>
+        <v>9026.09</v>
       </c>
     </row>
     <row r="357">
@@ -23654,7 +23654,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1088-31-CM26</t>
+          <t>3703-207-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23674,17 +23674,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>4255.46</v>
+        <v>6127.87</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3703-207-CM26</t>
+          <t>1088-31-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23739,17 +23739,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23778,7 +23778,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>6127.87</v>
+        <v>4255.46</v>
       </c>
     </row>
     <row r="360">
@@ -24044,7 +24044,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1376-246-CM26</t>
+          <t>1556-112-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -24103,13 +24103,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>6710.06</v>
+        <v>3914.2</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1556-112-CM26</t>
+          <t>1376-246-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24134,12 +24134,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -24168,13 +24168,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>3914.2</v>
+        <v>6710.06</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5350-883-CM26</t>
+          <t>1088-44-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24194,17 +24194,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24233,13 +24233,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>3571.31</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1088-44-CM26</t>
+          <t>1558-139-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24264,12 +24264,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24298,13 +24298,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>3348.1</v>
+        <v>4017.72</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1558-139-CM26</t>
+          <t>5350-883-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24324,17 +24324,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>4017.72</v>
+        <v>3571.31</v>
       </c>
     </row>
     <row r="369">
@@ -24694,7 +24694,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>3703-233-CM26</t>
+          <t>4357-123-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24719,12 +24719,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24753,13 +24753,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>6373.56</v>
+        <v>2747.22</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>4357-123-CM26</t>
+          <t>3703-233-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24784,12 +24784,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24818,13 +24818,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2747.22</v>
+        <v>6373.56</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2322-285-CM26</t>
+          <t>2859-339-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24849,12 +24849,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24883,13 +24883,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>38658.66</v>
+        <v>4418.13</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2859-339-CM26</t>
+          <t>2322-285-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24914,12 +24914,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -24948,7 +24948,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>4418.13</v>
+        <v>38658.66</v>
       </c>
     </row>
     <row r="378">
@@ -25864,7 +25864,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2859-431-CM26</t>
+          <t>4355-503-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25884,17 +25884,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25923,13 +25923,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>2906.1</v>
+        <v>4470.92</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>696011-24-CM26</t>
+          <t>1638-271-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25949,17 +25949,17 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.250.500-k</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25988,13 +25988,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>4365.86</v>
+        <v>3353.19</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1638-271-CM26</t>
+          <t>696011-24-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -26014,17 +26014,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>69.250.500-k</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -26053,13 +26053,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>3353.19</v>
+        <v>4365.86</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>4355-503-CM26</t>
+          <t>2859-431-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -26079,17 +26079,17 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -26118,7 +26118,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>4470.92</v>
+        <v>2906.1</v>
       </c>
     </row>
     <row r="396">
@@ -26579,7 +26579,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>4357-157-CM26</t>
+          <t>645-15-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26604,12 +26604,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.802.003-7</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -26638,13 +26638,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>11182.06</v>
+        <v>3913.72</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>645-15-CM26</t>
+          <t>4357-157-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26669,12 +26669,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>61.802.003-7</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26703,7 +26703,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>3913.72</v>
+        <v>11182.06</v>
       </c>
     </row>
     <row r="405">
@@ -27099,7 +27099,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>3703-333-CM26</t>
+          <t>4484-64-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -27124,12 +27124,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -27158,13 +27158,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>7062.16</v>
+        <v>6671.86</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>4484-64-CM26</t>
+          <t>3703-333-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27189,12 +27189,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27223,7 +27223,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>6671.86</v>
+        <v>7062.16</v>
       </c>
     </row>
     <row r="413">
@@ -27294,7 +27294,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1558-218-CM26</t>
+          <t>1376-412-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27319,12 +27319,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27353,13 +27353,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>4074.89</v>
+        <v>3102.54</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1376-412-CM26</t>
+          <t>1558-218-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27384,12 +27384,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27418,7 +27418,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3102.54</v>
+        <v>4074.89</v>
       </c>
     </row>
     <row r="416">
@@ -27944,7 +27944,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>4192-70-CM26</t>
+          <t>3703-368-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -27964,17 +27964,17 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -27984,17 +27984,17 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -28003,13 +28003,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>32548.55</v>
+        <v>6891.61</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2923-488-CM26</t>
+          <t>1638-329-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28029,17 +28029,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.250.500-k</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -28068,13 +28068,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2712.38</v>
+        <v>3254.86</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1638-329-CM26</t>
+          <t>2923-488-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -28094,17 +28094,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>69.250.500-k</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -28133,13 +28133,13 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>3254.86</v>
+        <v>2712.38</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>3703-368-CM26</t>
+          <t>4192-70-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -28159,17 +28159,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -28179,17 +28179,17 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -28198,7 +28198,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>6891.61</v>
+        <v>32548.55</v>
       </c>
     </row>
     <row r="428">
@@ -28594,7 +28594,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>4355-688-CM26</t>
+          <t>1556-196-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -28614,17 +28614,17 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -28653,13 +28653,13 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>4325.35</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>1556-196-CM26</t>
+          <t>4355-688-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -28679,17 +28679,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -28718,7 +28718,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>3244.01</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="436">
@@ -28919,7 +28919,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>3703-389-CM26</t>
+          <t>2380-1316-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28944,12 +28944,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28978,13 +28978,13 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>7495.29</v>
+        <v>36405.69</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2380-1316-CM26</t>
+          <t>3703-389-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -29009,12 +29009,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -29043,7 +29043,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>36405.69</v>
+        <v>7495.29</v>
       </c>
     </row>
     <row r="441">
@@ -29114,7 +29114,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>411-323-CM26</t>
+          <t>2381-858-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -29139,12 +29139,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -29173,7 +29173,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2304.79</v>
+        <v>21439.9</v>
       </c>
     </row>
     <row r="443">
@@ -29244,7 +29244,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2381-858-CM26</t>
+          <t>411-323-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -29269,12 +29269,12 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -29303,7 +29303,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>21439.9</v>
+        <v>2304.79</v>
       </c>
     </row>
     <row r="445">
@@ -29569,7 +29569,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>1556-214-CM26</t>
+          <t>1376-533-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -29594,12 +29594,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -29628,13 +29628,13 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>3244.01</v>
+        <v>6488.03</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>1376-533-CM26</t>
+          <t>1556-214-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -29659,12 +29659,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -29693,7 +29693,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>6488.03</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="451">
@@ -29829,7 +29829,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2923-569-CM26</t>
+          <t>2923-567-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29888,13 +29888,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>4935.46</v>
+        <v>16451.52</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1554-1357-CM26</t>
+          <t>2923-569-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -29953,13 +29953,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>14005.73</v>
+        <v>4935.46</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2923-567-CM26</t>
+          <t>1554-1357-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29984,12 +29984,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -30018,7 +30018,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>16451.52</v>
+        <v>14005.73</v>
       </c>
     </row>
     <row r="456">
@@ -30934,7 +30934,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>1088-97-CM26</t>
+          <t>873-37-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -30959,12 +30959,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -30993,7 +30993,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>5981.26</v>
+        <v>2413.79</v>
       </c>
     </row>
     <row r="471">
@@ -31064,7 +31064,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>873-37-CM26</t>
+          <t>1088-97-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -31089,12 +31089,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -31123,7 +31123,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>2413.79</v>
+        <v>5981.26</v>
       </c>
     </row>
     <row r="473">
@@ -31649,7 +31649,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>1248-9-CM26</t>
+          <t>1554-1534-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -31669,17 +31669,17 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>60.805.004-3</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -31708,13 +31708,13 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>2321.62</v>
+        <v>14812.18</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1612-105-CM26</t>
+          <t>1248-9-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -31729,22 +31729,22 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>60.511.030-4</t>
+          <t>60.805.004-3</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -31773,13 +31773,13 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>3779.82</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2923-683-CM26</t>
+          <t>1612-105-CM26</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -31804,12 +31804,12 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>60.511.030-4</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -31838,13 +31838,13 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>4801.69</v>
+        <v>3779.82</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2923-682-CM26</t>
+          <t>1556-249-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -31864,17 +31864,17 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -31903,7 +31903,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>16005.63</v>
+        <v>3201.13</v>
       </c>
     </row>
     <row r="485">
@@ -31974,7 +31974,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>1556-249-CM26</t>
+          <t>2923-682-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -31994,17 +31994,17 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -32033,13 +32033,13 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>3201.13</v>
+        <v>16005.63</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>5349-1851-CM26</t>
+          <t>2923-683-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -32054,7 +32054,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -32098,13 +32098,13 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>5314</v>
+        <v>4801.69</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>4192-112-CM26</t>
+          <t>5349-1851-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -32119,7 +32119,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -32129,12 +32129,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -32144,17 +32144,17 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -32163,13 +32163,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>31401.45</v>
+        <v>5314</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2322-772-CM26</t>
+          <t>4192-112-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -32184,22 +32184,22 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -32209,17 +32209,17 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -32228,13 +32228,13 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>3130.15</v>
+        <v>31401.45</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2859-1059-CM26</t>
+          <t>2322-772-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -32249,7 +32249,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -32259,12 +32259,12 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -32293,13 +32293,13 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>3541.71</v>
+        <v>3130.15</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>1088-128-CM26</t>
+          <t>2859-1059-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -32314,7 +32314,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -32324,12 +32324,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -32358,13 +32358,13 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>6149.53</v>
+        <v>3541.71</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>4881-86-CM26</t>
+          <t>1088-128-CM26</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -32389,12 +32389,12 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>65.511.520-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -32423,13 +32423,13 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2605.82</v>
+        <v>6149.53</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>1558-352-CM26</t>
+          <t>4881-86-CM26</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -32454,12 +32454,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>65.511.520-k</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -32488,13 +32488,13 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>3727.83</v>
+        <v>2605.82</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>1552-489-CM26</t>
+          <t>1558-352-CM26</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -32514,17 +32514,17 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -32553,13 +32553,13 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>11908.34</v>
+        <v>3727.83</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>1556-260-CM26</t>
+          <t>1552-489-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -32584,12 +32584,12 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>2578.12</v>
+        <v>11908.34</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2579-40-CM26</t>
+          <t>1556-260-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32649,12 +32649,12 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -32683,72 +32683,1697 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>3196.87</v>
+        <v>2578.12</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
+          <t>2579-40-CM26</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M497" s="2" t="n">
+        <v>3196.87</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
           <t>5350-1525-CM26</t>
         </is>
       </c>
-      <c r="B497" t="inlineStr">
+      <c r="B498" t="inlineStr">
         <is>
           <t>2239-13-LR25</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr">
+      <c r="C498" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr">
+      <c r="D498" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E497" t="inlineStr">
+      <c r="E498" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F497" t="inlineStr">
+      <c r="F498" t="inlineStr">
         <is>
           <t>69.030.500-3</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr">
+      <c r="G498" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I497" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J497" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K497" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L497" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M497" s="2" t="n">
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M498" s="2" t="n">
         <v>4740.02</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>4355-899-CM26</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>69.030.600-k</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M499" s="2" t="n">
+        <v>4112.69</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>3703-553-CM26</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>69.030.700-6</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M500" s="2" t="n">
+        <v>7566.87</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>1552-505-CM26</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>61.606.300-6</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M501" s="2" t="n">
+        <v>11689.95</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2322-823-CM26</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>69.030.500-3</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M502" s="2" t="n">
+        <v>18082.44</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>1557-358-CM26</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>61.606.309-k</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M503" s="2" t="n">
+        <v>6199.69</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>1376-715-CM26</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M504" s="2" t="n">
+        <v>6123.39</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2175-362-CM26</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M505" s="2" t="n">
+        <v>2205.08</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2380-1824-CM26</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M506" s="2" t="n">
+        <v>34636.97</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2926-209-CM26</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M507" s="2" t="n">
+        <v>6112.41</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>1554-1704-CM26</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M508" s="2" t="n">
+        <v>3616.91</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>751-382-CM26</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M509" s="2" t="n">
+        <v>5065.7</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>1556-284-CM26</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>61.606.305-7</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M510" s="2" t="n">
+        <v>2540.42</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>1671-259-CM26</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M511" s="2" t="n">
+        <v>9145.5</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>1729-465-CM26</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>69.030.400-7</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M512" s="2" t="n">
+        <v>21542.75</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2000-32-CM26</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>61.923.000-0</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M513" s="2" t="n">
+        <v>3157.95</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2923-788-CM26</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M514" s="2" t="n">
+        <v>2546.73</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2923-789-CM26</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M515" s="2" t="n">
+        <v>15280.4</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>1558-385-CM26</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>61.606.306-5</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M516" s="2" t="n">
+        <v>3667.29</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2859-1343-CM26</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M517" s="2" t="n">
+        <v>3769.16</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>4484-143-CM26</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>69.030.400-7</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M518" s="2" t="n">
+        <v>6110.85</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>1638-584-CM26</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>69.250.500-k</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M519" s="2" t="n">
+        <v>13284.83</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>1028871-656-CM26</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>61.999.330-6</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M520" s="2" t="n">
+        <v>5118.65</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>3703-592-CM26</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>69.030.700-6</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M521" s="2" t="n">
+        <v>7783.42</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>3332-119-CM26</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>69.251.900-0</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M522" s="2" t="n">
+        <v>2534.01</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/atacama.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M525"/>
+  <dimension ref="A1:M526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12344,7 +12344,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>873-47-CM25</t>
+          <t>4355-992-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12364,17 +12364,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12384,12 +12384,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3094.51</v>
+        <v>3457.41</v>
       </c>
     </row>
     <row r="185">
@@ -12474,7 +12474,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4355-992-CM25</t>
+          <t>873-47-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12494,17 +12494,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12514,12 +12514,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3457.41</v>
+        <v>3094.51</v>
       </c>
     </row>
     <row r="187">
@@ -21119,7 +21119,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5350-693-CM26</t>
+          <t>2923-123-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21139,17 +21139,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21178,13 +21178,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>3265</v>
+        <v>15158.94</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2923-123-CM26</t>
+          <t>5350-693-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21204,17 +21204,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>15158.94</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="321">
@@ -21704,7 +21704,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5349-530-CM26</t>
+          <t>1556-75-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21763,13 +21763,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>5470.58</v>
+        <v>3282.35</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1556-75-CM26</t>
+          <t>5349-530-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21794,12 +21794,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3282.35</v>
+        <v>5470.58</v>
       </c>
     </row>
     <row r="330">
@@ -21964,7 +21964,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2926-38-CM26</t>
+          <t>1558-102-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21989,12 +21989,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>6575.99</v>
+        <v>2849.6</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1558-102-CM26</t>
+          <t>2926-38-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22088,7 +22088,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>2849.6</v>
+        <v>6575.99</v>
       </c>
     </row>
     <row r="334">
@@ -22679,7 +22679,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2380-618-CM26</t>
+          <t>1556-96-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22699,17 +22699,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22738,13 +22738,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>36869.56</v>
+        <v>3795.4</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1556-96-CM26</t>
+          <t>2380-618-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22764,17 +22764,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22803,7 +22803,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>3795.4</v>
+        <v>36869.56</v>
       </c>
     </row>
     <row r="345">
@@ -23004,7 +23004,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1346283-70-CM26</t>
+          <t>1612-27-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -23024,17 +23024,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.511.030-4</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -23063,13 +23063,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>2384.59</v>
+        <v>3251.72</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1612-27-CM26</t>
+          <t>1346283-70-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -23089,17 +23089,17 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>60.511.030-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -23128,7 +23128,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>3251.72</v>
+        <v>2384.59</v>
       </c>
     </row>
     <row r="350">
@@ -23979,7 +23979,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2923-298-CM26</t>
+          <t>2923-300-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>16758.47</v>
+        <v>5586.16</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2923-300-CM26</t>
+          <t>2923-298-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -24103,7 +24103,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>5586.16</v>
+        <v>16758.47</v>
       </c>
     </row>
     <row r="365">
@@ -24239,7 +24239,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1088-44-CM26</t>
+          <t>5350-883-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24259,17 +24259,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>3348.1</v>
+        <v>3571.31</v>
       </c>
     </row>
     <row r="368">
@@ -24369,7 +24369,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5350-883-CM26</t>
+          <t>1088-44-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24389,17 +24389,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24428,7 +24428,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>3571.31</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="370">
@@ -24759,7 +24759,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>4357-123-CM26</t>
+          <t>3703-233-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24784,12 +24784,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24818,13 +24818,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2747.22</v>
+        <v>6373.56</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>3703-233-CM26</t>
+          <t>4357-123-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24849,12 +24849,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>6373.56</v>
+        <v>2747.22</v>
       </c>
     </row>
     <row r="377">
@@ -25474,7 +25474,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1376-322-CM26</t>
+          <t>411-223-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25494,17 +25494,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25533,13 +25533,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2336.06</v>
+        <v>22038.32</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>411-223-CM26</t>
+          <t>1376-322-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25559,17 +25559,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25598,7 +25598,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>22038.32</v>
+        <v>2336.06</v>
       </c>
     </row>
     <row r="388">
@@ -26514,7 +26514,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1556-155-CM26</t>
+          <t>3703-298-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26534,17 +26534,17 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -26573,13 +26573,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>3919.77</v>
+        <v>7111.58</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>3703-298-CM26</t>
+          <t>1556-155-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26599,17 +26599,17 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -26638,7 +26638,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>7111.58</v>
+        <v>3919.77</v>
       </c>
     </row>
     <row r="404">
@@ -27164,7 +27164,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>4484-64-CM26</t>
+          <t>3703-333-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27189,12 +27189,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27223,13 +27223,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>6671.86</v>
+        <v>7062.16</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>3703-333-CM26</t>
+          <t>4484-64-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27254,12 +27254,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>7062.16</v>
+        <v>6671.86</v>
       </c>
     </row>
     <row r="414">
@@ -27359,7 +27359,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1376-412-CM26</t>
+          <t>1558-218-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27384,12 +27384,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27418,13 +27418,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3102.54</v>
+        <v>4074.89</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1558-218-CM26</t>
+          <t>1376-412-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27449,12 +27449,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27483,7 +27483,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>4074.89</v>
+        <v>3102.54</v>
       </c>
     </row>
     <row r="417">
@@ -27684,7 +27684,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1556-175-CM26</t>
+          <t>4355-643-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27704,17 +27704,17 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27743,13 +27743,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>3271.64</v>
+        <v>4362.19</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>4355-643-CM26</t>
+          <t>1557-237-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27769,17 +27769,17 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27808,7 +27808,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>4362.19</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="422">
@@ -27879,7 +27879,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1557-237-CM26</t>
+          <t>1556-175-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27904,12 +27904,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27938,7 +27938,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>5452.74</v>
+        <v>3271.64</v>
       </c>
     </row>
     <row r="424">
@@ -28009,7 +28009,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>3703-368-CM26</t>
+          <t>1638-329-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28029,17 +28029,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.250.500-k</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>6891.61</v>
+        <v>3254.86</v>
       </c>
     </row>
     <row r="426">
@@ -28269,7 +28269,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1638-329-CM26</t>
+          <t>3703-368-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28289,17 +28289,17 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>69.250.500-k</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE DIEGO DE ALMAGRO</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>3254.86</v>
+        <v>6891.61</v>
       </c>
     </row>
     <row r="430">
@@ -28659,7 +28659,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>1556-196-CM26</t>
+          <t>4355-688-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -28679,17 +28679,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -28718,13 +28718,13 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>3244.01</v>
+        <v>4325.35</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>4355-688-CM26</t>
+          <t>1556-196-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -28744,17 +28744,17 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -28783,7 +28783,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>4325.35</v>
+        <v>3244.01</v>
       </c>
     </row>
     <row r="437">
@@ -28919,7 +28919,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1729-297-CM26</t>
+          <t>2380-1316-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28944,12 +28944,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28978,7 +28978,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>22485.87</v>
+        <v>36405.69</v>
       </c>
     </row>
     <row r="440">
@@ -29049,7 +29049,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2380-1316-CM26</t>
+          <t>1729-297-CM26</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -29108,7 +29108,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>36405.69</v>
+        <v>22485.87</v>
       </c>
     </row>
     <row r="442">
@@ -29244,7 +29244,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2381-858-CM26</t>
+          <t>411-322-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -29269,12 +29269,12 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -29303,13 +29303,13 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>21439.9</v>
+        <v>10719.95</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>411-322-CM26</t>
+          <t>2381-858-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -29334,12 +29334,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -29368,7 +29368,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>10719.95</v>
+        <v>21439.9</v>
       </c>
     </row>
     <row r="446">
@@ -29439,7 +29439,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>1373324-56-CM26</t>
+          <t>904-115-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -29464,12 +29464,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -29498,13 +29498,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2325.24</v>
+        <v>10400.26</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>667-27-CM26</t>
+          <t>1373324-56-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -29524,17 +29524,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>61.938.700-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>2272.39</v>
+        <v>2325.24</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>904-115-CM26</t>
+          <t>667-27-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -29589,17 +29589,17 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.938.700-7</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -29628,7 +29628,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>10400.26</v>
+        <v>2272.39</v>
       </c>
     </row>
     <row r="450">
@@ -30154,7 +30154,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>5350-1291-CM26</t>
+          <t>4484-102-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -30179,12 +30179,12 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -30213,13 +30213,13 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>5020.19</v>
+        <v>5456.73</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>4484-102-CM26</t>
+          <t>5350-1291-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -30244,12 +30244,12 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -30278,7 +30278,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>5456.73</v>
+        <v>5020.19</v>
       </c>
     </row>
     <row r="460">
@@ -30544,7 +30544,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>1490607-13-CM26</t>
+          <t>1558-304-CM26</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -30564,17 +30564,17 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -30603,13 +30603,13 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>24489.71</v>
+        <v>3942.18</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>1558-304-CM26</t>
+          <t>1490607-13-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30629,17 +30629,17 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -30668,7 +30668,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>3942.18</v>
+        <v>24489.71</v>
       </c>
     </row>
     <row r="466">
@@ -30804,7 +30804,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>4355-728-CM26</t>
+          <t>3332-90-CM26</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -30863,13 +30863,13 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>2331.01</v>
+        <v>4337.83</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>3332-90-CM26</t>
+          <t>4355-728-CM26</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -30894,12 +30894,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -30928,13 +30928,13 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>4337.83</v>
+        <v>2331.01</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>1346283-224-CM26</t>
+          <t>2859-905-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -30959,12 +30959,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -30993,13 +30993,13 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2396.07</v>
+        <v>2777.26</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2859-905-CM26</t>
+          <t>1346283-224-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -31024,12 +31024,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -31058,13 +31058,13 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>2777.26</v>
+        <v>2396.07</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>1088-97-CM26</t>
+          <t>873-36-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -31089,12 +31089,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -31123,7 +31123,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>5981.26</v>
+        <v>2413.79</v>
       </c>
     </row>
     <row r="473">
@@ -31194,7 +31194,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>873-36-CM26</t>
+          <t>1088-97-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -31219,12 +31219,12 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -31253,7 +31253,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>2413.79</v>
+        <v>5981.26</v>
       </c>
     </row>
     <row r="475">
@@ -32624,7 +32624,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>1552-489-CM26</t>
+          <t>1558-352-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32649,12 +32649,12 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -32683,13 +32683,13 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>11908.34</v>
+        <v>3727.83</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1558-352-CM26</t>
+          <t>1552-489-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>3727.83</v>
+        <v>11908.34</v>
       </c>
     </row>
     <row r="498">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
@@ -34569,6 +34569,71 @@
       </c>
       <c r="M525" s="2" t="n">
         <v>3040.81</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>1557-379-CM26</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>61.606.309-k</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M526" s="2" t="n">
+        <v>12116.93</v>
       </c>
     </row>
   </sheetData>
